--- a/registration_forms/005_adr_networking_event_application--registration_forms.xlsx
+++ b/registration_forms/005_adr_networking_event_application--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,8 +934,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -963,12 +963,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'mediator',_'value':_'mediator'}</t>
+          <t>mediator</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Mediator', 'value': 'mediator'}</t>
+          <t>Mediator</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'arbitrator',_'value':_'arbitrator'}</t>
+          <t>arbitrator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Arbitrator', 'value': 'arbitrator'}</t>
+          <t>Arbitrator</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'attorney',_'value':_'attorney'}</t>
+          <t>attorney</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Attorney', 'value': 'attorney'}</t>
+          <t>Attorney</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'academic',_'value':_'academic'}</t>
+          <t>academic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Academic', 'value': 'academic'}</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'student',_'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Student', 'value': 'student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'commercial_mediation',_'value':_'commercial'}</t>
+          <t>commercial_mediation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial Mediation', 'value': 'commercial'}</t>
+          <t>Commercial Mediation</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'family_law',_'value':_'family'}</t>
+          <t>family_law</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Family Law', 'value': 'family'}</t>
+          <t>Family Law</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'labor_and_employment',_'value':_'labor'}</t>
+          <t>labor_and_employment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Labor and Employment', 'value': 'labor'}</t>
+          <t>Labor and Employment</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'international_arbitration',_'value':_'international'}</t>
+          <t>international_arbitration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'International Arbitration', 'value': 'international'}</t>
+          <t>International Arbitration</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'community_mediation',_'value':_'community'}</t>
+          <t>community_mediation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Community Mediation', 'value': 'community'}</t>
+          <t>Community Mediation</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'online_dispute_resolution_(odr)',_'value':_'odr'}</t>
+          <t>online_dispute_resolution_(odr)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Online Dispute Resolution (ODR)', 'value': 'odr'}</t>
+          <t>Online Dispute Resolution (ODR)</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_mediation_techniques',_'value':_'advanced_mediation'}</t>
+          <t>advanced_mediation_techniques</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced Mediation Techniques', 'value': 'advanced_mediation'}</t>
+          <t>Advanced Mediation Techniques</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'the_future_of_arbitration',_'value':_'future_arbitration'}</t>
+          <t>the_future_of_arbitration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'The Future of Arbitration', 'value': 'future_arbitration'}</t>
+          <t>The Future of Arbitration</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'ethics_in_adr',_'value':_'ethics'}</t>
+          <t>ethics_in_adr</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Ethics in ADR', 'value': 'ethics'}</t>
+          <t>Ethics in ADR</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'building_a_successful_adr_practice',_'value':_'practice_building'}</t>
+          <t>building_a_successful_adr_practice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Building a Successful ADR Practice', 'value': 'practice_building'}</t>
+          <t>Building a Successful ADR Practice</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian', 'value': 'vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan', 'value': 'vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'gluten-free',_'value':_'gluten_free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Gluten-Free', 'value': 'gluten_free'}</t>
+          <t>Gluten-Free</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'dairy-free',_'value':_'dairy_free'}</t>
+          <t>dairy-free</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Dairy-Free', 'value': 'dairy_free'}</t>
+          <t>Dairy-Free</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'nut_allergy',_'value':_'nut_allergy'}</t>
+          <t>nut_allergy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Nut Allergy', 'value': 'nut_allergy'}</t>
+          <t>Nut Allergy</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'email_invitation',_'value':_'email'}</t>
+          <t>email_invitation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Email Invitation', 'value': 'email'}</t>
+          <t>Email Invitation</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'linkedin',_'value':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'LinkedIn', 'value': 'linkedin'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'colleague_referral',_'value':_'colleague'}</t>
+          <t>colleague_referral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Colleague Referral', 'value': 'colleague'}</t>
+          <t>Colleague Referral</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'bar_association_website',_'value':_'bar_association'}</t>
+          <t>bar_association_website</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Bar Association Website', 'value': 'bar_association'}</t>
+          <t>Bar Association Website</t>
         </is>
       </c>
     </row>
